--- a/files/Formula Excel Template.xlsx
+++ b/files/Formula Excel Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/Excel Series Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\advance_excel\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEE5DA8A-F772-4B0E-A554-1053E2C64027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D12FF-D302-4CFA-8033-B06E862AE2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="9" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Max-Min" sheetId="9" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="LeftRight" sheetId="4" r:id="rId4"/>
     <sheet name="DateToText" sheetId="3" r:id="rId5"/>
     <sheet name="TRIM" sheetId="6" r:id="rId6"/>
-    <sheet name="Substitute" sheetId="7" r:id="rId7"/>
-    <sheet name="SUM-SumIF" sheetId="12" r:id="rId8"/>
-    <sheet name="Count-CountIF" sheetId="5" r:id="rId9"/>
-    <sheet name="Concatenate" sheetId="1" r:id="rId10"/>
+    <sheet name="Concatenate" sheetId="1" r:id="rId7"/>
+    <sheet name="Substitute" sheetId="7" r:id="rId8"/>
+    <sheet name="SUM-SumIF" sheetId="12" r:id="rId9"/>
+    <sheet name="Count-CountIF" sheetId="5" r:id="rId10"/>
     <sheet name="Days-NetworkDays" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -43,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="89">
   <si>
     <t>FirstName</t>
   </si>
@@ -308,6 +330,9 @@
   </si>
   <si>
     <t>Right</t>
+  </si>
+  <si>
+    <t>5-6/2001</t>
   </si>
 </sst>
 </file>
@@ -349,10 +374,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -372,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -412,7 +436,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -518,7 +542,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -660,7 +684,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -741,8 +765,14 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1">
+        <f>MAX(H2:H10)</f>
+        <v>37933</v>
+      </c>
+      <c r="K2" s="1">
+        <f>MIN(H2:H10)</f>
+        <v>35040</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -772,8 +802,14 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="J3">
+        <f>MAX(G2:G10)</f>
+        <v>65000</v>
+      </c>
+      <c r="K3">
+        <f>MIN(G2:G10)</f>
+        <v>36000</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -984,22 +1020,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB977C31-5FD1-4473-A6A1-29ABAD3F7755}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D217F6E-9452-40AF-AFA2-377600A25F44}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1028,10 +1060,16 @@
         <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="K1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1059,8 +1097,20 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <f>COUNT(G2:G10)</f>
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIF(G2:G10,"&gt;42000")</f>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <f>COUNTIFS(E2:E10,"Male")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1089,7 +1139,7 @@
         <v>42287</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1118,7 +1168,7 @@
         <v>42986</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1147,7 +1197,7 @@
         <v>42341</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -1176,7 +1226,7 @@
         <v>42977</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -1205,7 +1255,7 @@
         <v>41528</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -1234,7 +1284,7 @@
         <v>41551</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -1263,7 +1313,7 @@
         <v>42116</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1290,18 +1340,6 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H11" t="str">
-        <f t="shared" ref="H3:H12" si="0">CONCATENATE(B11," ",C11)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H12" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
@@ -1340,7 +1378,7 @@
       <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
@@ -1375,13 +1413,13 @@
       <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>45000</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1404,13 +1442,13 @@
       <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>36000</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1433,13 +1471,13 @@
       <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>63000</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1462,13 +1500,13 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <v>47000</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1491,13 +1529,13 @@
       <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <v>50000</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1520,13 +1558,13 @@
       <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>65000</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1549,13 +1587,13 @@
       <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>41000</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1578,13 +1616,13 @@
       <c r="F9" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9">
         <v>48000</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1607,13 +1645,13 @@
       <c r="F10" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>42000</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1698,6 +1736,14 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">IF(D2:D10&gt;30,"OLD","YOUNG")</f>
+        <v>YOUNG</v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2:K10">_xlfn.IFS(F2:F10="Salesman","Sales",F2:F10="HR","Fire Immediately")</f>
+        <v>Sales</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1727,6 +1773,12 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3" t="str">
+        <v>YOUNG</v>
+      </c>
+      <c r="K3" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1756,6 +1808,12 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4" t="str">
+        <v>YOUNG</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Sales</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1785,6 +1843,12 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="K5" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1814,6 +1878,12 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Fire Immediately</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1843,6 +1913,12 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="K7" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1872,6 +1948,12 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="K8" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1901,6 +1983,12 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Sales</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1929,6 +2017,12 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>OLD</v>
+      </c>
+      <c r="K10" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -2010,6 +2104,10 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2" cm="1">
+        <f t="array" ref="J2:J10">LEN(C2:C10)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -2039,6 +2137,9 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -2068,6 +2169,9 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -2097,6 +2201,9 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -2126,6 +2233,9 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -2155,6 +2265,9 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -2184,6 +2297,9 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -2213,6 +2329,9 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -2241,6 +2360,9 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2323,14 +2445,26 @@
       <c r="G2">
         <v>45000</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>39</v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" ref="K2:K10">LEFT(B2:B10,3)</f>
+        <v>Jim</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">RIGHT(A2:A10,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M2" t="str" cm="1">
+        <f t="array" ref="M2:M10">RIGHT(H2:H10,4)</f>
+        <v>2001</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -2355,14 +2489,23 @@
       <c r="G3">
         <v>36000</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pam</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2</v>
+      </c>
+      <c r="M3" t="str">
+        <v>1999</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -2387,14 +2530,23 @@
       <c r="G4">
         <v>63000</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>41</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Dwi</v>
+      </c>
+      <c r="L4" t="str">
+        <v>3</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -2419,14 +2571,23 @@
       <c r="G5">
         <v>47000</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>42</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Ang</v>
+      </c>
+      <c r="L5" t="str">
+        <v>4</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -2451,14 +2612,23 @@
       <c r="G6">
         <v>50000</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Tob</v>
+      </c>
+      <c r="L6" t="str">
+        <v>5</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2001</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -2483,14 +2653,23 @@
       <c r="G7">
         <v>65000</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>44</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Mic</v>
+      </c>
+      <c r="L7" t="str">
+        <v>6</v>
+      </c>
+      <c r="M7" t="str">
+        <v>2001</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -2515,14 +2694,23 @@
       <c r="G8">
         <v>41000</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>45</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Mer</v>
+      </c>
+      <c r="L8" t="str">
+        <v>7</v>
+      </c>
+      <c r="M8" t="str">
+        <v>2003</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -2547,14 +2735,23 @@
       <c r="G9">
         <v>48000</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Sta</v>
+      </c>
+      <c r="L9" t="str">
+        <v>8</v>
+      </c>
+      <c r="M9" t="str">
+        <v>2002</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -2579,14 +2776,23 @@
       <c r="G10">
         <v>42000</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>47</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Kev</v>
+      </c>
+      <c r="L10" t="str">
+        <v>9</v>
+      </c>
+      <c r="M10" t="str">
+        <v>2003</v>
       </c>
     </row>
   </sheetData>
@@ -2599,14 +2805,14 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2638,7 +2844,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2666,9 +2872,16 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">TEXT(H2:H10,"dd/mm/yyyy")</f>
+        <v>02/11/2001</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">RIGHT(_xlfn.ANCHORARRAY(J2),4)</f>
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -2696,9 +2909,14 @@
       <c r="I3" s="1">
         <v>42287</v>
       </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J3" t="str">
+        <v>03/10/1999</v>
+      </c>
+      <c r="L3" t="str">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -2726,9 +2944,14 @@
       <c r="I4" s="1">
         <v>42986</v>
       </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J4" t="str">
+        <v>04/07/2000</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -2756,9 +2979,14 @@
       <c r="I5" s="1">
         <v>42341</v>
       </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J5" t="str">
+        <v>05/01/2000</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -2786,9 +3014,14 @@
       <c r="I6" s="1">
         <v>42977</v>
       </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J6" t="str">
+        <v>06/05/2001</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -2816,9 +3049,14 @@
       <c r="I7" s="1">
         <v>41528</v>
       </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J7" t="str">
+        <v>07/12/1995</v>
+      </c>
+      <c r="L7" t="str">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -2846,9 +3084,14 @@
       <c r="I8" s="1">
         <v>41551</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J8" t="str">
+        <v>08/11/2003</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -2876,9 +3119,14 @@
       <c r="I9" s="1">
         <v>42116</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J9" t="str">
+        <v>09/06/2002</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -2906,13 +3154,18 @@
       <c r="I10" s="1">
         <v>40800</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J10" t="str">
+        <v>10/08/2003</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H13" s="3"/>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2970,10 +3223,10 @@
       <c r="A2">
         <v>1001</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2">
@@ -2993,16 +3246,20 @@
       </c>
       <c r="I2" s="1">
         <v>42253</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">TRIM(C2:C10)</f>
+        <v>Halpert</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3">
@@ -3022,16 +3279,19 @@
       </c>
       <c r="I3" s="1">
         <v>42287</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Beasley</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D4">
@@ -3051,16 +3311,19 @@
       </c>
       <c r="I4" s="1">
         <v>42986</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Schrute</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D5">
@@ -3080,16 +3343,19 @@
       </c>
       <c r="I5" s="1">
         <v>42341</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Martin</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D6">
@@ -3109,16 +3375,19 @@
       </c>
       <c r="I6" s="1">
         <v>42977</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Flenderson</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D7">
@@ -3138,16 +3407,19 @@
       </c>
       <c r="I7" s="1">
         <v>41528</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Scott</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D8">
@@ -3167,16 +3439,19 @@
       </c>
       <c r="I8" s="1">
         <v>41551</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Palmer</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D9">
@@ -3196,16 +3471,19 @@
       </c>
       <c r="I9" s="1">
         <v>42116</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Hudson</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D10">
@@ -3225,6 +3503,9 @@
       </c>
       <c r="I10" s="1">
         <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Malone</v>
       </c>
     </row>
   </sheetData>
@@ -3233,6 +3514,393 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB977C31-5FD1-4473-A6A1-29ABAD3F7755}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <v>45000</v>
+      </c>
+      <c r="H2" s="1">
+        <v>37197</v>
+      </c>
+      <c r="I2" s="1">
+        <v>42253</v>
+      </c>
+      <c r="J2" t="str">
+        <f>_xlfn.CONCAT(B2," ",C2)</f>
+        <v>Jim Halpert</v>
+      </c>
+      <c r="K2" t="str">
+        <f>_xlfn.CONCAT(B2,".",C2,"@gmail.com")</f>
+        <v>Jim.Halpert@gmail.com</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3">
+        <v>36000</v>
+      </c>
+      <c r="H3" s="1">
+        <v>36436</v>
+      </c>
+      <c r="I3" s="1">
+        <v>42287</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J10" si="0">_xlfn.CONCAT(B3," ",C3)</f>
+        <v>Pam Beasley</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K10" si="1">_xlfn.CONCAT(B3,".",C3,"@gmail.com")</f>
+        <v>Pam.Beasley@gmail.com</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>63000</v>
+      </c>
+      <c r="H4" s="1">
+        <v>36711</v>
+      </c>
+      <c r="I4" s="1">
+        <v>42986</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>Dwight Schrute</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="1"/>
+        <v>Dwight.Schrute@gmail.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>47000</v>
+      </c>
+      <c r="H5" s="1">
+        <v>36530</v>
+      </c>
+      <c r="I5" s="1">
+        <v>42341</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>Angela Martin</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
+        <v>Angela.Martin@gmail.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>50000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>37017</v>
+      </c>
+      <c r="I6" s="1">
+        <v>42977</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>Toby Flenderson</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
+        <v>Toby.Flenderson@gmail.com</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>65000</v>
+      </c>
+      <c r="H7" s="1">
+        <v>35040</v>
+      </c>
+      <c r="I7" s="1">
+        <v>41528</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>Michael Scott</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="1"/>
+        <v>Michael.Scott@gmail.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>41000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>37933</v>
+      </c>
+      <c r="I8" s="1">
+        <v>41551</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>Meredith Palmer</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="1"/>
+        <v>Meredith.Palmer@gmail.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>48000</v>
+      </c>
+      <c r="H9" s="1">
+        <v>37416</v>
+      </c>
+      <c r="I9" s="1">
+        <v>42116</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>Stanley Hudson</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="1"/>
+        <v>Stanley.Hudson@gmail.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10">
+        <v>42000</v>
+      </c>
+      <c r="H10" s="1">
+        <v>37843</v>
+      </c>
+      <c r="I10" s="1">
+        <v>40800</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>Kevin Malone</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="1"/>
+        <v>Kevin.Malone@gmail.com</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0B9C42-087D-43BC-95CC-49AE54CDC17A}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -3242,7 +3910,6 @@
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -3264,7 +3931,7 @@
       <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
@@ -3302,14 +3969,18 @@
       <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2">
         <v>45000</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>56</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">SUBSTITUTE(H2:H10,"-","/")</f>
+        <v>11/2/2001</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -3331,14 +4002,17 @@
       <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>36000</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>57</v>
+      </c>
+      <c r="J3" t="str">
+        <v>10/3/1999</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -3360,14 +4034,17 @@
       <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>63000</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="J4" t="str">
+        <v>7/4/2000</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -3389,14 +4066,17 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5">
         <v>47000</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="J5" t="str">
+        <v>1/5/2000</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -3418,14 +4098,17 @@
       <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <v>50000</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="H6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="J6" t="str">
+        <v>5/6/2001</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -3447,14 +4130,17 @@
       <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>65000</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>61</v>
+      </c>
+      <c r="J7" t="str">
+        <v>5/6/2001</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -3476,14 +4162,17 @@
       <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>41000</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>61</v>
+      </c>
+      <c r="J8" t="str">
+        <v>11/8/2003</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -3505,14 +4194,17 @@
       <c r="F9" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9">
         <v>48000</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="J9" t="str">
+        <v>6/9/2002</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -3534,51 +4226,54 @@
       <c r="F10" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>42000</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="J10" t="str">
+        <v>8/10/2003</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
     </row>
     <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3586,7 +4281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D41C5D0-EC67-4288-8B29-30C6E5CFEE73}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -3660,321 +4355,17 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3">
-        <v>36000</v>
-      </c>
-      <c r="H3" s="1">
-        <v>36436</v>
-      </c>
-      <c r="I3" s="1">
-        <v>42287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4">
-        <v>63000</v>
-      </c>
-      <c r="H4" s="1">
-        <v>36711</v>
-      </c>
-      <c r="I4" s="1">
-        <v>42986</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5">
-        <v>47000</v>
-      </c>
-      <c r="H5" s="1">
-        <v>36530</v>
-      </c>
-      <c r="I5" s="1">
-        <v>42341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>50000</v>
-      </c>
-      <c r="H6" s="1">
-        <v>37017</v>
-      </c>
-      <c r="I6" s="1">
-        <v>42977</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7">
-        <v>65000</v>
-      </c>
-      <c r="H7" s="1">
-        <v>35040</v>
-      </c>
-      <c r="I7" s="1">
-        <v>41528</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8">
+      <c r="J2">
+        <f>SUM(G2:G10)</f>
+        <v>437000</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(G2:G10,"&gt;50000")</f>
+        <v>128000</v>
+      </c>
+      <c r="L2">
+        <f>SUMIFS(G2:G10,E2:E10,"Female",D2:D10,"&gt;31")</f>
         <v>41000</v>
-      </c>
-      <c r="H8" s="1">
-        <v>37933</v>
-      </c>
-      <c r="I8" s="1">
-        <v>41551</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9">
-        <v>48000</v>
-      </c>
-      <c r="H9" s="1">
-        <v>37416</v>
-      </c>
-      <c r="I9" s="1">
-        <v>42116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10">
-        <v>42000</v>
-      </c>
-      <c r="H10" s="1">
-        <v>37843</v>
-      </c>
-      <c r="I10" s="1">
-        <v>40800</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D217F6E-9452-40AF-AFA2-377600A25F44}">
-  <sheetPr>
-    <tabColor theme="9"/>
-  </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2">
-        <v>45000</v>
-      </c>
-      <c r="H2" s="1">
-        <v>37197</v>
-      </c>
-      <c r="I2" s="1">
-        <v>42253</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">

--- a/files/Formula Excel Template.xlsx
+++ b/files/Formula Excel Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\advance_excel\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D12FF-D302-4CFA-8033-B06E862AE2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3286DEE0-6635-419D-873E-2FBCBA80E755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="9" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="10" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Max-Min" sheetId="9" r:id="rId1"/>
@@ -1422,6 +1422,14 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="J2">
+        <f>_xlfn.DAYS(I2,H2)</f>
+        <v>5231</v>
+      </c>
+      <c r="K2">
+        <f>NETWORKDAYS(H2,I2)</f>
+        <v>3737</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
